--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_18-07-2025.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£3.75</t>
+          <t>£10.8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£4.07</t>
+          <t>£11.72</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -638,25 +638,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -726,7 +726,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£4.95</t>
+          <t>£14.26</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -739,25 +739,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -827,7 +827,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£5.63</t>
+          <t>£16.21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -840,25 +840,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -928,7 +928,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£6.77</t>
+          <t>£19.5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -941,25 +941,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£7.55</t>
+          <t>£21.74</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1042,25 +1042,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£8.01</t>
+          <t>£23.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1143,25 +1143,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£8.83</t>
+          <t>£25.43</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1244,25 +1244,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£9.52</t>
+          <t>£27.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1345,25 +1345,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£9.84</t>
+          <t>£28.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£10.91</t>
+          <t>£31.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1547,25 +1547,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£11.92</t>
+          <t>£34.33</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1648,25 +1648,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£14.24</t>
+          <t>£41.01</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£12.89</t>
+          <t>£37.12</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1826,25 +1826,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£13.89</t>
+          <t>£40.0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1927,25 +1927,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>£14.93</t>
+          <t>£43.0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2028,25 +2028,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff61c57e925+77845]
-	GetHandleVerifier [0x0x7ff61c57e980+77936]
-	(No symbol) [0x0x7ff61c339cda]
-	(No symbol) [0x0x7ff61c3906aa]
-	(No symbol) [0x0x7ff61c39095c]
-	(No symbol) [0x0x7ff61c3e3d07]
-	(No symbol) [0x0x7ff61c3b890f]
-	(No symbol) [0x0x7ff61c3e0b07]
-	(No symbol) [0x0x7ff61c3b86a3]
-	(No symbol) [0x0x7ff61c381791]
-	(No symbol) [0x0x7ff61c382523]
-	GetHandleVerifier [0x0x7ff61c85683d+3059501]
-	GetHandleVerifier [0x0x7ff61c850bfd+3035885]
-	GetHandleVerifier [0x0x7ff61c8703f0+3164896]
-	GetHandleVerifier [0x0x7ff61c598c2e+185118]
-	GetHandleVerifier [0x0x7ff61c5a053f+216111]
-	GetHandleVerifier [0x0x7ff61c5872d4+113092]
-	GetHandleVerifier [0x0x7ff61c587489+113529]
-	GetHandleVerifier [0x0x7ff61c56e288+10616]
+	GetHandleVerifier [0x0x7ff78f3fe925+77845]
+	GetHandleVerifier [0x0x7ff78f3fe980+77936]
+	(No symbol) [0x0x7ff78f1b9cda]
+	(No symbol) [0x0x7ff78f2106aa]
+	(No symbol) [0x0x7ff78f21095c]
+	(No symbol) [0x0x7ff78f263d07]
+	(No symbol) [0x0x7ff78f23890f]
+	(No symbol) [0x0x7ff78f260b07]
+	(No symbol) [0x0x7ff78f2386a3]
+	(No symbol) [0x0x7ff78f201791]
+	(No symbol) [0x0x7ff78f202523]
+	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
+	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
+	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
+	GetHandleVerifier [0x0x7ff78f418c2e+185118]
+	GetHandleVerifier [0x0x7ff78f42053f+216111]
+	GetHandleVerifier [0x0x7ff78f4072d4+113092]
+	GetHandleVerifier [0x0x7ff78f407489+113529]
+	GetHandleVerifier [0x0x7ff78f3ee288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>

--- a/Compititor's_Price/Unilin_Prices/Unilin_Prices_18-07-2025.xlsx
+++ b/Compititor's_Price/Unilin_Prices/Unilin_Prices_18-07-2025.xlsx
@@ -518,17 +518,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>£11.15</t>
+          <t>£10.98</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -595,17 +595,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>£12.80</t>
+          <t>£12.62</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -638,25 +638,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -696,17 +696,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>£16.46</t>
+          <t>£16.18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -739,25 +739,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -840,25 +840,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -898,17 +898,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>£21.20</t>
+          <t>£21.08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -941,25 +941,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -999,17 +999,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>£23.13</t>
+          <t>£22.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1042,25 +1042,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1143,25 +1143,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1244,25 +1244,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.82</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1345,25 +1345,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>£29.00</t>
+          <t>£28.99</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1446,25 +1446,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1547,25 +1547,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1605,17 +1605,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>£35.85</t>
+          <t>£34.99</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1648,25 +1648,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1826,25 +1826,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -1884,17 +1884,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>£44.50</t>
+          <t>£43.99</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1927,25 +1927,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
@@ -2028,25 +2028,25 @@
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
   (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff78f3fe925+77845]
-	GetHandleVerifier [0x0x7ff78f3fe980+77936]
-	(No symbol) [0x0x7ff78f1b9cda]
-	(No symbol) [0x0x7ff78f2106aa]
-	(No symbol) [0x0x7ff78f21095c]
-	(No symbol) [0x0x7ff78f263d07]
-	(No symbol) [0x0x7ff78f23890f]
-	(No symbol) [0x0x7ff78f260b07]
-	(No symbol) [0x0x7ff78f2386a3]
-	(No symbol) [0x0x7ff78f201791]
-	(No symbol) [0x0x7ff78f202523]
-	GetHandleVerifier [0x0x7ff78f6d683d+3059501]
-	GetHandleVerifier [0x0x7ff78f6d0bfd+3035885]
-	GetHandleVerifier [0x0x7ff78f6f03f0+3164896]
-	GetHandleVerifier [0x0x7ff78f418c2e+185118]
-	GetHandleVerifier [0x0x7ff78f42053f+216111]
-	GetHandleVerifier [0x0x7ff78f4072d4+113092]
-	GetHandleVerifier [0x0x7ff78f407489+113529]
-	GetHandleVerifier [0x0x7ff78f3ee288+10616]
+	GetHandleVerifier [0x0x7ff6890be925+77845]
+	GetHandleVerifier [0x0x7ff6890be980+77936]
+	(No symbol) [0x0x7ff688e79cda]
+	(No symbol) [0x0x7ff688ed06aa]
+	(No symbol) [0x0x7ff688ed095c]
+	(No symbol) [0x0x7ff688f23d07]
+	(No symbol) [0x0x7ff688ef890f]
+	(No symbol) [0x0x7ff688f20b07]
+	(No symbol) [0x0x7ff688ef86a3]
+	(No symbol) [0x0x7ff688ec1791]
+	(No symbol) [0x0x7ff688ec2523]
+	GetHandleVerifier [0x0x7ff68939683d+3059501]
+	GetHandleVerifier [0x0x7ff689390bfd+3035885]
+	GetHandleVerifier [0x0x7ff6893b03f0+3164896]
+	GetHandleVerifier [0x0x7ff6890d8c2e+185118]
+	GetHandleVerifier [0x0x7ff6890e053f+216111]
+	GetHandleVerifier [0x0x7ff6890c72d4+113092]
+	GetHandleVerifier [0x0x7ff6890c7489+113529]
+	GetHandleVerifier [0x0x7ff6890ae288+10616]
 	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
 	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
 </t>
